--- a/99_Others/Supplement.xlsx
+++ b/99_Others/Supplement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\99_Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC4FA4B-AE6D-4855-8D3A-444BA7080C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A7E020-252E-4BD4-90CC-896D05F491CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
@@ -8268,26 +8268,6 @@
     <phoneticPr fontId="17"/>
   </si>
   <si>
-    <t>・マルウェア対策のためマクロ自動実行ブロックのまま閲覧する習慣あり
-・多人数で共有を考慮して「新規」や「読み取り専用」で開く習慣あり</t>
-    <rPh sb="29" eb="31">
-      <t>シュウカン</t>
-    </rPh>
-    <rPh sb="35" eb="38">
-      <t>タニンズウ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>キョウユウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>コウリョ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>シュウカン</t>
-    </rPh>
-    <phoneticPr fontId="17"/>
-  </si>
-  <si>
     <t>WebLogic</t>
     <phoneticPr fontId="17"/>
   </si>
@@ -9283,6 +9263,36 @@
     </rPh>
     <rPh sb="210" eb="212">
       <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>・マルウェア対策のためマクロ自動実行ブロックのまま閲覧する習慣あり
+・多人数で共有を考慮して「新規」や「読み取り専用」で開く習慣あり
+・グラフィックアクセラレータを無効にする設定をする習慣あり</t>
+    <rPh sb="29" eb="31">
+      <t>シュウカン</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>タニンズウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>コウリョ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>シュウカン</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ムコウ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>シュウカン</t>
     </rPh>
     <phoneticPr fontId="17"/>
   </si>
@@ -11229,22 +11239,22 @@
     </row>
     <row r="5" spans="1:7" ht="75.75" thickTop="1">
       <c r="A5" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>489</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>490</v>
-      </c>
       <c r="C5" s="38" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E5" s="16">
         <v>1</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G5" s="15">
         <v>46198</v>
@@ -11252,22 +11262,22 @@
     </row>
     <row r="6" spans="1:7" ht="150">
       <c r="A6" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="38" t="s">
+        <v>485</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>480</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>486</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>481</v>
       </c>
       <c r="E6" s="16">
         <v>2</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G6" s="15">
         <v>46128</v>
@@ -11798,10 +11808,10 @@
         <v>92</v>
       </c>
       <c r="C5" s="20" t="s">
+        <v>495</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>496</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>497</v>
       </c>
       <c r="E5" s="23" t="s">
         <v>434</v>
@@ -11824,7 +11834,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>436</v>
@@ -11850,7 +11860,7 @@
         <v>107</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D7" s="43" t="s">
         <v>313</v>
@@ -12253,7 +12263,7 @@
         <v>114</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>115</v>
@@ -12696,10 +12706,10 @@
         <v>132</v>
       </c>
       <c r="B35" s="20" t="s">
+        <v>482</v>
+      </c>
+      <c r="C35" s="20" t="s">
         <v>483</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>484</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>129</v>
@@ -12967,7 +12977,7 @@
         <v>167</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>161</v>
@@ -12993,7 +13003,7 @@
         <v>201</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>161</v>
@@ -13233,7 +13243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="37.5">
+    <row r="20" spans="1:8" ht="56.25">
       <c r="A20" s="13" t="s">
         <v>185</v>
       </c>
@@ -13241,7 +13251,7 @@
         <v>184</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>161</v>
@@ -13363,7 +13373,7 @@
     </row>
     <row r="25" spans="1:8" ht="75">
       <c r="A25" s="20" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B25" s="20" t="s">
         <v>190</v>
@@ -13421,7 +13431,7 @@
         <v>194</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>161</v>
@@ -13537,7 +13547,7 @@
         <v>198</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D32" s="23" t="s">
         <v>161</v>
@@ -13643,13 +13653,13 @@
     </row>
     <row r="37" spans="1:8" ht="56.25">
       <c r="A37" s="20" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B37" s="20" t="s">
         <v>203</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>161</v>
@@ -13821,7 +13831,7 @@
     </row>
     <row r="45" spans="1:8" ht="37.5">
       <c r="A45" s="20" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B45" s="20" t="s">
         <v>391</v>
@@ -14113,13 +14123,13 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="B58" s="20" t="s">
         <v>474</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="C58" s="20" t="s">
         <v>475</v>
-      </c>
-      <c r="C58" s="20" t="s">
-        <v>476</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>161</v>
@@ -14135,10 +14145,10 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C59" s="20"/>
       <c r="D59" s="23"/>
@@ -14956,12 +14966,12 @@
     </row>
     <row r="39" spans="2:12">
       <c r="C39" s="39" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="40" spans="2:12">
       <c r="C40" s="40" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -14975,7 +14985,7 @@
       </c>
       <c r="L42" s="34">
         <f ca="1">TODAY()</f>
-        <v>46264</v>
+        <v>46271</v>
       </c>
     </row>
   </sheetData>
